--- a/backend-excel/data/bets.xlsx
+++ b/backend-excel/data/bets.xlsx
@@ -397,75 +397,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J2"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>id</v>
-      </c>
-      <c r="B1" t="str">
-        <v>date</v>
-      </c>
-      <c r="C1" t="str">
-        <v>name</v>
-      </c>
-      <c r="D1" t="str">
-        <v>username</v>
-      </c>
-      <c r="E1" t="str">
-        <v>matchId</v>
-      </c>
-      <c r="F1" t="str">
-        <v>matchName</v>
-      </c>
-      <c r="G1" t="str">
-        <v>betType</v>
-      </c>
-      <c r="H1" t="str">
-        <v>stake</v>
-      </c>
-      <c r="I1" t="str">
-        <v>status</v>
-      </c>
-      <c r="J1" t="str">
-        <v>payout</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>dbd9cb82-a62a-4660-b2e6-2ecf9aa00d3c</v>
-      </c>
-      <c r="B2" t="str">
-        <v>2026-06-04T13:45:31.513Z</v>
-      </c>
-      <c r="C2" t="str">
-        <v>luanluan</v>
-      </c>
-      <c r="D2" t="str">
-        <v>lctran</v>
-      </c>
-      <c r="E2" t="str">
-        <v>2</v>
-      </c>
-      <c r="F2" t="str">
-        <v>South Korea vs Czechia</v>
-      </c>
-      <c r="G2" t="str">
-        <v>homeWin</v>
-      </c>
-      <c r="H2">
-        <v>10000</v>
-      </c>
-      <c r="I2" t="str">
-        <v>pending</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
+  <dimension ref="A1"/>
+  <sheetData/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/backend-excel/data/bets.xlsx
+++ b/backend-excel/data/bets.xlsx
@@ -397,10 +397,235 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetData/>
+  <dimension ref="A1:J7"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>DATE</v>
+      </c>
+      <c r="C1" t="str">
+        <v>NAME</v>
+      </c>
+      <c r="D1" t="str">
+        <v>USERNAME</v>
+      </c>
+      <c r="E1" t="str">
+        <v>MATCHID</v>
+      </c>
+      <c r="F1" t="str">
+        <v>MATCHNAME</v>
+      </c>
+      <c r="G1" t="str">
+        <v>BETTYPE</v>
+      </c>
+      <c r="H1" t="str">
+        <v>STAKE</v>
+      </c>
+      <c r="I1" t="str">
+        <v>STATUS</v>
+      </c>
+      <c r="J1" t="str">
+        <v>PAYOUT</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>c977bfd5-38ab-4067-aa44-297c228dc3ae</v>
+      </c>
+      <c r="B2" t="str">
+        <v>2026-06-04T14:32:31.390Z</v>
+      </c>
+      <c r="C2" t="str">
+        <v>luanluan</v>
+      </c>
+      <c r="D2" t="str">
+        <v>lctran</v>
+      </c>
+      <c r="E2" t="str">
+        <v>2</v>
+      </c>
+      <c r="F2" t="str">
+        <v>South Korea vs Czechia</v>
+      </c>
+      <c r="G2" t="str">
+        <v>South Korea</v>
+      </c>
+      <c r="H2">
+        <v>10000</v>
+      </c>
+      <c r="I2" t="str">
+        <v>pending</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>8c7ab6b1-4907-42c8-8abb-dedc04cc11ec</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-06-04T14:32:40.099Z</v>
+      </c>
+      <c r="C3" t="str">
+        <v>luanluan</v>
+      </c>
+      <c r="D3" t="str">
+        <v>lctran</v>
+      </c>
+      <c r="E3" t="str">
+        <v>1</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Mexico vs South Africa</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Mexico</v>
+      </c>
+      <c r="H3">
+        <v>10000</v>
+      </c>
+      <c r="I3" t="str">
+        <v>pending</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>c91a0779-06c4-402f-9ba0-a0edc534b568</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-06-04T14:32:42.031Z</v>
+      </c>
+      <c r="C4" t="str">
+        <v>luanluan</v>
+      </c>
+      <c r="D4" t="str">
+        <v>lctran</v>
+      </c>
+      <c r="E4" t="str">
+        <v>3</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Canada vs Bosnia-Herzegovina</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Canada</v>
+      </c>
+      <c r="H4">
+        <v>10000</v>
+      </c>
+      <c r="I4" t="str">
+        <v>pending</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>fcb191f6-6855-4bcc-81e4-00a67bf69ca7</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-06-04T14:32:43.885Z</v>
+      </c>
+      <c r="C5" t="str">
+        <v>luanluan</v>
+      </c>
+      <c r="D5" t="str">
+        <v>lctran</v>
+      </c>
+      <c r="E5" t="str">
+        <v>4</v>
+      </c>
+      <c r="F5" t="str">
+        <v>USA vs Paraguay</v>
+      </c>
+      <c r="G5" t="str">
+        <v>USA</v>
+      </c>
+      <c r="H5">
+        <v>10000</v>
+      </c>
+      <c r="I5" t="str">
+        <v>pending</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>739d4d33-2834-4419-aad4-75759fb176b7</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-06-04T14:32:46.182Z</v>
+      </c>
+      <c r="C6" t="str">
+        <v>luanluan</v>
+      </c>
+      <c r="D6" t="str">
+        <v>lctran</v>
+      </c>
+      <c r="E6" t="str">
+        <v>8</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Qatar vs Switzerland</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Qatar</v>
+      </c>
+      <c r="H6">
+        <v>10000</v>
+      </c>
+      <c r="I6" t="str">
+        <v>pending</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>789438e7-36c0-4c98-b8af-5ab5a75475c6</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-06-04T14:32:47.847Z</v>
+      </c>
+      <c r="C7" t="str">
+        <v>luanluan</v>
+      </c>
+      <c r="D7" t="str">
+        <v>lctran</v>
+      </c>
+      <c r="E7" t="str">
+        <v>7</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Brazil vs Morocco</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Brazil</v>
+      </c>
+      <c r="H7">
+        <v>10000</v>
+      </c>
+      <c r="I7" t="str">
+        <v>pending</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/backend-excel/data/bets.xlsx
+++ b/backend-excel/data/bets.xlsx
@@ -397,10 +397,107 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetData/>
+  <dimension ref="A1:J3"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>DATE</v>
+      </c>
+      <c r="C1" t="str">
+        <v>NAME</v>
+      </c>
+      <c r="D1" t="str">
+        <v>USERNAME</v>
+      </c>
+      <c r="E1" t="str">
+        <v>MATCHID</v>
+      </c>
+      <c r="F1" t="str">
+        <v>MATCHNAME</v>
+      </c>
+      <c r="G1" t="str">
+        <v>BETTYPE</v>
+      </c>
+      <c r="H1" t="str">
+        <v>STAKE</v>
+      </c>
+      <c r="I1" t="str">
+        <v>STATUS</v>
+      </c>
+      <c r="J1" t="str">
+        <v>PAYOUT</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>cc22e3a7-2765-468f-8079-a5b79b5b2439</v>
+      </c>
+      <c r="B2" t="str">
+        <v>2026-06-12T04:05:07.083Z</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Nguyen Van A</v>
+      </c>
+      <c r="D2" t="str">
+        <v>test</v>
+      </c>
+      <c r="E2" t="str">
+        <v>2</v>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v>South Korea</v>
+      </c>
+      <c r="H2">
+        <v>10000</v>
+      </c>
+      <c r="I2" t="str">
+        <v>won</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>d1cd2c0a-877f-4f6f-8ada-7b3b9d966be7</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-06-12T04:05:07.177Z</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Nguyen Van B</v>
+      </c>
+      <c r="D3" t="str">
+        <v>cam</v>
+      </c>
+      <c r="E3" t="str">
+        <v>2</v>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v>Czechia</v>
+      </c>
+      <c r="H3">
+        <v>10000</v>
+      </c>
+      <c r="I3" t="str">
+        <v>lost</v>
+      </c>
+      <c r="J3">
+        <v>-10000</v>
+      </c>
+    </row>
+  </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/backend-excel/data/bets.xlsx
+++ b/backend-excel/data/bets.xlsx
@@ -397,107 +397,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J3"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>ID</v>
-      </c>
-      <c r="B1" t="str">
-        <v>DATE</v>
-      </c>
-      <c r="C1" t="str">
-        <v>NAME</v>
-      </c>
-      <c r="D1" t="str">
-        <v>USERNAME</v>
-      </c>
-      <c r="E1" t="str">
-        <v>MATCHID</v>
-      </c>
-      <c r="F1" t="str">
-        <v>MATCHNAME</v>
-      </c>
-      <c r="G1" t="str">
-        <v>BETTYPE</v>
-      </c>
-      <c r="H1" t="str">
-        <v>STAKE</v>
-      </c>
-      <c r="I1" t="str">
-        <v>STATUS</v>
-      </c>
-      <c r="J1" t="str">
-        <v>PAYOUT</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>cc22e3a7-2765-468f-8079-a5b79b5b2439</v>
-      </c>
-      <c r="B2" t="str">
-        <v>2026-06-12T04:05:07.083Z</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Nguyen Van A</v>
-      </c>
-      <c r="D2" t="str">
-        <v>test</v>
-      </c>
-      <c r="E2" t="str">
-        <v>2</v>
-      </c>
-      <c r="F2" t="str">
-        <v/>
-      </c>
-      <c r="G2" t="str">
-        <v>South Korea</v>
-      </c>
-      <c r="H2">
-        <v>10000</v>
-      </c>
-      <c r="I2" t="str">
-        <v>won</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>d1cd2c0a-877f-4f6f-8ada-7b3b9d966be7</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-06-12T04:05:07.177Z</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Nguyen Van B</v>
-      </c>
-      <c r="D3" t="str">
-        <v>cam</v>
-      </c>
-      <c r="E3" t="str">
-        <v>2</v>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v>Czechia</v>
-      </c>
-      <c r="H3">
-        <v>10000</v>
-      </c>
-      <c r="I3" t="str">
-        <v>lost</v>
-      </c>
-      <c r="J3">
-        <v>-10000</v>
-      </c>
-    </row>
-  </sheetData>
+  <dimension ref="A1"/>
+  <sheetData/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1"/>
   </ignoredErrors>
 </worksheet>
 </file>